--- a/public/insurepro_엑셀등록.xlsx
+++ b/public/insurepro_엑셀등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82102\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kne/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90E2AF80-31CA-4E45-8246-787E86310B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E65E5C8-E5F9-8746-BA06-0797ED96AD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{924AA513-BDC7-4131-B75D-FD5DDC101F72}"/>
+    <workbookView xWindow="39320" yWindow="5240" windowWidth="23260" windowHeight="12460" xr2:uid="{924AA513-BDC7-4131-B75D-FD5DDC101F72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -104,7 +103,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;₩&quot;#,##0_);[Red]\(&quot;₩&quot;#,##0\)"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,7 +294,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -311,14 +313,38 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -337,15 +363,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -667,41 +684,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{028543B7-2E9C-46DE-A66A-65252BB1EC8E}">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="18.296875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" style="3"/>
-    <col min="3" max="3" width="8.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.69921875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.8984375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.3984375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="21.5" style="3" customWidth="1"/>
-    <col min="8" max="8" width="22.3984375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" style="13"/>
+    <col min="3" max="3" width="8.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="15" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="13" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" ht="37" thickBot="1">
+      <c r="A1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="16" t="s">
         <v>1</v>
       </c>
       <c r="J1" s="4"/>
@@ -709,25 +726,25 @@
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="J2" s="9" t="s">
+    <row r="2" spans="1:15">
+      <c r="J2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="11"/>
-    </row>
-    <row r="3" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="J3" s="12"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="14"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="19"/>
+    </row>
+    <row r="3" spans="1:15" ht="18" thickBot="1">
+      <c r="J3" s="20"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="22"/>
+    </row>
+    <row r="4" spans="1:15">
       <c r="J4" s="5"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
@@ -735,7 +752,7 @@
       <c r="N4" s="8"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15">
       <c r="J5" s="5" t="s">
         <v>6</v>
       </c>
@@ -745,7 +762,7 @@
       <c r="N5" s="8"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15">
       <c r="J6" s="5" t="s">
         <v>7</v>
       </c>
@@ -755,7 +772,7 @@
       <c r="N6" s="8"/>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15">
       <c r="J7" s="5" t="s">
         <v>8</v>
       </c>
@@ -765,7 +782,7 @@
       <c r="N7" s="8"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15">
       <c r="J8" s="5" t="s">
         <v>12</v>
       </c>
@@ -775,7 +792,7 @@
       <c r="N8" s="8"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15">
       <c r="J9" s="5" t="s">
         <v>13</v>
       </c>
@@ -785,7 +802,7 @@
       <c r="N9" s="8"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15">
       <c r="J10" s="5"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
@@ -793,15 +810,15 @@
       <c r="N10" s="8"/>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="J11" s="15" t="s">
+    <row r="11" spans="1:15" ht="18" thickBot="1">
+      <c r="J11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="17"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
